--- a/MATRIZ_MAESTRA_DECISIONES_Trazabilidad.xlsx
+++ b/MATRIZ_MAESTRA_DECISIONES_Trazabilidad.xlsx
@@ -470,10 +470,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -496,10 +496,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -522,7 +522,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>32</v>
@@ -548,7 +548,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -574,7 +574,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>25</v>
@@ -626,7 +626,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>8</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -730,7 +730,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>6</v>
@@ -756,7 +756,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -782,7 +782,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>80</v>
@@ -860,7 +860,7 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>13</v>
@@ -886,7 +886,7 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>266</v>
@@ -938,7 +938,7 @@
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>41</v>
@@ -964,7 +964,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>69</v>
@@ -990,7 +990,7 @@
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>21</v>
@@ -1016,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>4</v>
@@ -1042,7 +1042,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>60</v>
@@ -1068,7 +1068,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>13</v>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1120,7 +1120,7 @@
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>115</v>
@@ -1172,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1198,7 +1198,7 @@
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>96</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>19</v>
@@ -1250,7 +1250,7 @@
         <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>0.225</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>16</v>
@@ -1275,7 +1275,9 @@
       <c r="C33" t="n">
         <v>1</v>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" t="n">
         <v>18</v>
       </c>
@@ -1300,7 +1302,7 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>76</v>
@@ -1326,7 +1328,7 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -1390,3621 +1392,3744 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>N°</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Municipio</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Municipio</t>
+          <t>Parroquia</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Parroquia</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>ID Infraestructura</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>ID Infraestructura</t>
+          <t>Cuenta con Evaluación de Habitabilidad por la CPEHI</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Cuenta con Evaluación de Habitabilidad por la CPEHI</t>
+          <t>Tipo de Urbanismo</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tipo de Urbanismo</t>
+          <t>Cantidad de Edificios existentes</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Cantidad de Edificios existentes</t>
+          <t>Cantidad de Edificios en Reconstrucción</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Cantidad de Edificios en Reconstrucción</t>
+          <t>Cantidad de Viviendas existentes</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Cantidad de Viviendas existentes</t>
+          <t>Tipo de Vivienda</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Tipo de Vivienda</t>
+          <t>Cantidad de Viviendas en Reconstrucción</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Cantidad de Viviendas en Reconstrucción</t>
+          <t>% Avance Físico
+de Obra de Reconstrucción</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>% Avance Físico de Obra de Reconstrucción</t>
+          <t>Cantidad de Viviendas en Demolición</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Cantidad de Viviendas en Demolición</t>
+          <t>% Avance Físico de Obra de Demolición</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>% Avance Físico de Obra de Demolición</t>
+          <t>Cantidad de Familias Afectadas</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Cantidad de Familias Afectadas</t>
+          <t>Ubicación (Dirección)</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Ubicación (Dirección)</t>
+          <t>Ejecutor Asignado</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Ejecutor Asignado</t>
+          <t>Contacto Institucional</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Contacto Institucional</t>
+          <t>Contacto de la Comunidad</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Contacto de la Comunidad</t>
+          <t>Longitud y Latitud</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DISTRITO CAPITAL</t>
+          <t>LIBERTADOR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>23 DE ENERO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CRISTO REY</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CONSEJO COMUNAL CRISTO REY</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>212</v>
+      </c>
+      <c r="J2" t="n">
+        <v>42</v>
+      </c>
+      <c r="K2" t="n">
+        <v>212</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>55</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P2" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>98</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Sector Cristo Rey</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>PROHABITAT LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>JOSE GREGORIO ROJAS EUGENIO 04141916837</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ana Caona 412-5787722</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>10.506276299213724, -66.93344240305352</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>LIBERTADOR</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>23 DE ENERO</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CRISTO REY</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>43 VIVIENDAS EN CRISTO REY</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>BLOQUES DE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Alcaldía de Caracas</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Caserio</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>43</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>casa</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>10</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>43</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Sector Cristo Rey</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>PROHABITAT LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>JOSE GREGORIO ROJAS EUGENIO 04141916837</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Barbara Hernandez 412-5787722</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>23 DE ENERO</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
           <t>Edificio Privado</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>22</v>
       </c>
       <c r="J3" t="n">
         <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+        <v>370</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>Apartamento</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
+      <c r="M3" t="n">
+        <v>25</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>0.15</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Sector La Libertad</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Sector La Libertad</t>
+          <t>PROHABITAT LIBERTADOR</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>PROHABITAT LIBERTADOR</t>
+          <t>JOSE GREGORIO ROJAS EUGENIO 04141916837</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>JOSE GREGORIO ROJAS EUGENIO 04141916837</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr"/>
+          <t>YUBIRI FONSECA 04261991748</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>10.503559853266438, -66.9310486024425</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DISTRITO CAPITAL</t>
+          <t>LIBERTADOR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LIBERTADOR</t>
+          <t>ALTAGRACIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ALTAGRACIA</t>
+          <t>ESQUINA SAN RAMÓN</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ESQUINA SAN RAMÓN</t>
+          <t>ACONCAGUA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ACONCAGUA</t>
+          <t>Alcaldía de Caracas</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
           <t>Edificio Privado</t>
         </is>
       </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
         <v>32</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Apartamento</t>
         </is>
       </c>
+      <c r="M4" t="n">
+        <v>32</v>
+      </c>
       <c r="N4" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>32</v>
       </c>
-      <c r="O4" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
-        <v>32</v>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>AV. FUERZAS ARMADAS CON AV. ESTE 5. ESQUINA SAN RAMÓN</t>
+        </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>AV. FUERZAS ARMADAS CON AV. ESTE 5. ESQUINA SAN RAMÓN</t>
+          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
-        <is>
-          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
         <is>
           <t>CARLOS SOTO
 0412-700 0849</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>CAROLINA CAPOTE
 0412-0483072</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>10.499488585007317, -66.87592346737343</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DISTRITO CAPITAL</t>
+          <t>LIBERTADOR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LIBERTADOR</t>
+          <t>CARICUAO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CARICUAO</t>
+          <t>Gran Base de Misión</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gran Base de Misión</t>
+          <t>Campamento Transitorio Gran Base de Paz Caricuao</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Campamento Transitorio Gran Base de Paz Caricuao</t>
+          <t>Alcaldía de Caracas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
           <t>Campamento</t>
         </is>
       </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Camas</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>300</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Camas</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>300</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Gimnasio vetical de Caricuao</t>
+        </is>
+      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Gimnasio vetical de Caricuao</t>
+          <t>Brisopp y Paneles Caracas</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>Orlando Tarazona (0414) 351.0959.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>10.474127425157453, -66.94525254794362</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CATEDRAL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV. BARALT </t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÁGUILA </t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Edificio Privado</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>20</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>25</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CALLE DE CONDE A PIÑANGO, PARROQUIA CATEDRAL </t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>BARWILL GONZÁLEZ 04141243722</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>MARIA MILLÁN 04241477745</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	
+10.499669118096678, -66.9099621745696</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>COCHE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>La Rinconada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Urbanización La Rinconada</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Edificio Privado</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>14</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>288</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>84</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>8</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Av Intercomunal El Valle. La rinconada</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>Brisopp y Paneles Caracas</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Orlando Tarazona (0414) 351.0959.</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Miriam Matos (0426) 605.0868.</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>10.445713225547667, -66.92430118593609</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>LIBERTADOR</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CATEDRAL</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AV. BARALT </t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ÁGUILA </t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>COCHE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Carlos Delgado Chalbaud</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>URB CARLOS DELGADO CHALBAUD</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Alcaldía de Caracas</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Edificio Privado</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>20</v>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Edificio Patrimonial</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>Apartamento</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>20</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="n">
-        <v>25</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CALLE DE CONDE A PIÑANGO, PARROQUIA CATEDRAL </t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>BARWILL GONZÁLEZ 04141243722</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>MARIA MILLÁN 04241477745</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Av intercomunal Valle- Coche, Resd La Rinconada zona 1, bloque 4, cerca de la estación de servicios Coche, frente a la Cancha de Lucas.</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Brisopp y Paneles Caracas</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Orlando Tarazona (0414) 351.0959.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>10.445341721751365, -66.92640685754401</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>LIBERTADOR</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>COCHE</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>La Rinconada</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Urbanización La Rinconada</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EL JUNQUITO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FABRICIO OJEDA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VIVIENDA MULTIFAMILIAR Km11</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Alcaldía de Caracas</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Edificio Privado</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>14</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>288</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>84</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="n">
-        <v>8</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Av Intercomunal El Valle. La rinconada</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Brisopp y Paneles Caracas</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Orlando Tarazona (0414) 351.0959.</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Miriam Matos (0426) 605.0868.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>COCHE</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Carlos Delgado Chalbaud</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>URB CARLOS DELGADO CHALBAUD</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Edificio Patrimonial</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Caserio</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Av intercomunal Valle- Coche, Resd La Rinconada zona 1, bloque 4, cerca de la estación de servicios Coche, frente a la Cancha de Lucas.</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Brisopp y Paneles Caracas</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Orlando Tarazona (0414) 351.0959.</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>EL JUNQUITO</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>FABRICIO OJEDA</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>VIVIENDA MULTIFAMILIAR Km11</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Caserio</t>
-        </is>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>casa</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
         <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>casa</t>
-        </is>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>CALLEJON NAIGUATA, BARRIO JOSE ANTONIO PAEZ, KM 11 EL JUNQUITO, SECTOR FABRICIO OJEDA.</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>BARWILL GONZALEZ 0414-1243722</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>ORLANDO SALCEDO 0424-3684347</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>10.477597670186407, -67.0070269018926</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>CALLEJON NAIGUATA, BARRIO JOSE ANTONIO PAEZ, KM 11 EL JUNQUITO, SECTOR FABRICIO OJEDA.</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>BARWILL GONZALEZ 0414-1243722</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>ORLANDO SALCEDO 0424-3684347</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="n">
-        <v>9</v>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DISTRITO CAPITAL</t>
+          <t>LIBERTADOR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LIBERTADOR</t>
+          <t>EL PARAISO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EL PARAISO</t>
+          <t>LAS FUENTES</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LAS FUENTES</t>
+          <t xml:space="preserve">SAN JUDAS TADEO (Colapso de Estructura) </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN JUDAS TADEO (Colapso de Estructura) </t>
+          <t>Alcaldía de Caracas</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
           <t>Edificio Privado</t>
         </is>
       </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
         <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
+        <v>7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Av. Las Fuentes</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>PROHABITAT LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>JOSE GREGORIO ROJAS EUGENIO 04141916837</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>10.483870414757819, -66.89706081428213</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Av. Las Fuentes</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>PROHABITAT LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>JOSE GREGORIO ROJAS EUGENIO 04141916837</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="n">
-        <v>10</v>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DISTRITO CAPITAL</t>
+          <t>LIBERTADOR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LIBERTADOR</t>
+          <t>EL RECREO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EL RECREO</t>
+          <t>QUEBRADA LAZARETO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>QUEBRADA LAZARETO</t>
+          <t>5 VIVIENDAS UNIFAMILIAR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5 VIVIENDAS UNIFAMILIAR</t>
+          <t>Alcaldía de Caracas</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
           <t>Caserio</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>casa</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>6</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>QUEBRADA LAZARETO, DETRAS DEL BLOQUE 3</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>BARWILL GONZALEZ 0414-1243722</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>YANTONELY GOMEZ 0414-2770100</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>10.508241823981605, -66.89228516878624</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>casa</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>QUEBRADA LAZARETO, DETRAS DEL BLOQUE 3</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>BARWILL GONZALEZ 0414-1243722</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>YANTONELY GOMEZ 0414-2770100</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="n">
-        <v>11</v>
-      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DISTRITO CAPITAL</t>
+          <t>LIBERTADOR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LIBERTADOR</t>
+          <t>EL RECREO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EL RECREO</t>
+          <t>Gran Base de Misión</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gran Base de Misión</t>
+          <t>Campamento Transitorio Gran Base de Paz Pinto Salina</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Campamento Transitorio Gran Base de Paz Pinto Salina</t>
+          <t>Alcaldía de Caracas</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
           <t>Campamento</t>
         </is>
       </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Camas</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>300</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Camas</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>300</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Gimnasio vetical del Recreo</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Gimnasio vetical del Recreo</t>
+          <t>Brisopp y Paneles Caracas</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Brisopp y Paneles Caracas</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
           <t>Orlando Tarazona (0414) 351.0959.</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>10.507421628005805, -66.88971106275805</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DISTRITO CAPITAL</t>
+          <t>LIBERTADOR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LIBERTADOR</t>
+          <t>EL VALLE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EL VALLE</t>
+          <t>Gran Base de Misión</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gran Base de Misión</t>
+          <t>Campamento Transitorio Gran Base de Paz EL Valle</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Campamento Transitorio Gran Base de Paz EL Valle</t>
+          <t>Alcaldía de Caracas</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
           <t>Campamento</t>
         </is>
       </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Camas</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>300</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Camas</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>300</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Gimnasio vetical del Recreo</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Gimnasio vetical del Recreo</t>
+          <t>Brisopp y Paneles Caracas</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Brisopp y Paneles Caracas</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
           <t>Orlando Tarazona (0414) 351.0959.</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>10.466415028689788, -66.94912729661121</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DISTRITO CAPITAL</t>
+          <t>LIBERTADOR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LIBERTADOR</t>
+          <t xml:space="preserve">LA CANDELARIA </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">LA CANDELARIA </t>
+          <t>SARRIA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SARRIA</t>
+          <t>Torre de David (Placa de estructura por colapsar)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Torre de David (Placa de estructura por colapsar)</t>
+          <t>Alcaldía de Caracas</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
           <t>BANCARIO</t>
         </is>
       </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PLACA DE ESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
         <v>0</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>PLACA DE ESTRUCTURA</t>
-        </is>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Av. Andres Bello</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>IMGRAD</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>IVAN MARTINEZ - 0412-0279209</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>10.505186122059804, -66.89875694134817</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Av. Andres Bello</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>IMGRAD</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>IVAN MARTINEZ - 0412-0279209</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">m </t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>14</v>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DISTRITO CAPITAL</t>
+          <t>LIBERTADOR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">LA CANDELARIA </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BELLAS ARTES</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDIFICIO CONTINENTE </t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Edificio Privado</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>52</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>12</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>80</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>AVENIDA MEXICO</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>PROHABITAT LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>JOSE GREGORIO ROJAS EUGENIO 04141916837</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>JESSICA FIGUEROA 04242918831</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>10.507571681307352, -66.95820319900581</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>LIBERTADOR</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LA CANDELARIA </t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>BELLAS ARTES</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EDIFICIO CONTINENTE </t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>La Pastora</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PUERTAS CARACAS</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U.E.P. Colegio Agustiniano San Judas Tadeo (Colapso de Estructura) </t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>Alcaldía de Caracas</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Edificio Privado</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>52</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>12</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="n">
-        <v>80</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>AVENIDA MEXICO</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>PROHABITAT LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>JOSE GREGORIO ROJAS EUGENIO 04141916837</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>JESSICA FIGUEROA 04242918831</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="n">
-        <v>15</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>La Pastora</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>PUERTAS CARACAS</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">U.E.P. Colegio Agustiniano San Judas Tadeo (Colapso de Estructura) </t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
           <t>Escuela</t>
         </is>
       </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>aula</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>aula</t>
-        </is>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
-        <v>0.53</v>
-      </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Matricula Escolar Afectada 1000 Alumnos</t>
+          <t>Calle Real Puerta Caracas, Comuna Camino de Independencia</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Calle Real Puerta Caracas, Comuna Camino de Independencia</t>
+          <t>Cuerpo de Ingenieros de la GNB (DICOI N° 43)</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Cuerpo de Ingenieros de la GNB (DICOI N° 43)</t>
+          <t>May. Delgado Ramirez Angel Jose 0424-4059210</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>May. Delgado Ramirez Angel Jose 0424-4059210</t>
+          <t>Ana Rey</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Ana Rey</t>
+          <t>10.520750957818068, -66.92070873897644</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DISTRITO CAPITAL</t>
+          <t>LIBERTADOR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LIBERTADOR</t>
+          <t>MACARAO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MACARAO</t>
+          <t>EL COPEY</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
-        <is>
-          <t>EL COPEY</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
         <is>
           <t>VIVIENDAS UNIFAMILIAR
 SECTOR FUENTE DE VIDA</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
           <t>Caserio</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>23</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>casa</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>23</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="n">
+        <v>13</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRETERA NACIONAL CARCAS-LOS TEQUES, SECTOR BARRIO EL COPEY, TIERRA BLANCA, PARROQUIA MACARAO </t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>BARWILL GONZALEZ 0414-1243722</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>ANGELA MARTINES  0424-1083820</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>10.394233300446537, -67.02205118231826</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>23</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>casa</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>23</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="n">
-        <v>13</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CARRETERA NACIONAL CARCAS-LOS TEQUES, SECTOR BARRIO EL COPEY, TIERRA BLANCA, PARROQUIA MACARAO </t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SAN AGUSTIN</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ÑO PASTOR</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>OMAR TORRIJOS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Edificio Privado</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>240</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>240</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="n">
+        <v>266</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AVENIDA BOLIVAR </t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>BARWILL GONZALEZ 0414-1243722</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>ANGELA MARTINES  0424-1083820</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="n">
-        <v>17</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>DAYANA CARBALLO 0414-9701176</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>10.50247284649156, -66.90623406075437</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>LIBERTADOR</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>SAN AGUSTIN</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÑO PASTOR</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>OMAR TORRIJOS</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>METRO CABLE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>METRO CABLE EL MANGUITO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>Alcaldía de Caracas</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Edificio Privado</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>240</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>240</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="n">
-        <v>266</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AVENIDA BOLIVAR </t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>BARWILL GONZALEZ 0414-1243722</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>DAYANA CARBALLO 0414-9701176</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="n">
-        <v>18</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>SAN AGUSTIN</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>METRO CABLE</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>METRO CABLE EL MANGUITO</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
           <t>Campamento</t>
         </is>
       </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>camas</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>300</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>camas</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>300</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>gimnasio vertical</t>
+        </is>
+      </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>gimnasio vertical</t>
+          <t>Brisopp y Paneles Caracas</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
+          <t>Orlando Tarazona (0414) 351.0959.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>10.494323056556475, -66.91878408504164</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SAN BERNARDINO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Av. La Estrella</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Urbanismo OPP 20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Urbanismo GMVV </t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>144</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>58</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="n">
+        <v>69</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Av. Estrella. San Bernardino </t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
           <t>Brisopp y Paneles Caracas</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Orlando Tarazona (0414) 351.0959.</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="n">
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lolimar Linarez (0412) 060.5978.</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>10.506873292887164, -66.90146039298855</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SAN BERNARDINO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LOS PROCERES</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Edificio Alfa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Edificio Privado</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Av. Principal de Residencia Anauco</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Brisopp y Paneles Caracas</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Orlando Tarazona (0414) 351.0959.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Rafael Quijada</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>10.514479472909349, -66.89788249636119</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SAN BERNARDINO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PARQUE RESIDENCIAL ANAUCO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ELITE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Edificio Privado</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>60</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>60</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="n">
+        <v>60</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>AVENIDA LOS PROCERES CON AV MARQUES DEL TORO, URB SAN BERNARDINO</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>BARWILL GONZALEZ 0414-1243722</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SORISBEL ARAUJO 0414-1343322</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>10.513197302786022, -66.89810018083783</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SAN BERNARDINO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AV. LOS PRÓCERES</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>MAROA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Edificio Privado</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
         <v>19</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>19</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="n">
+        <v>19</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>AVENIDA LOS PROCERES, URB SAN BERNARDINO</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>BARWILL GONZALEZ 0414-1243722</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>JORGE BECERRA 0424-6749271</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>10.514891169145354, -66.89771215469932</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>LIBERTADOR</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>SAN BERNARDINO</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Av. La Estrella</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Urbanismo OPP 20</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AV. LOS PRÓCERES</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MACTOR</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>Alcaldía de Caracas</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Urbanismo GMVV </t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>144</v>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Edificio Privado</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>22</v>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>Apartamento</t>
         </is>
       </c>
-      <c r="N20" t="n">
-        <v>58</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="n">
-        <v>69</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Av. Estrella. San Bernardino </t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Brisopp y Paneles Caracas</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Orlando Tarazona (0414) 351.0959.</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Lolimar Linarez (0412) 060.5978.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="n">
-        <v>20</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="M24" t="n">
+        <v>22</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="n">
+        <v>22</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>AVENIDA LOS PROCERES, URB SAN BERNARDINO</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>BARWILL GONZALEZ 0414-1243722</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>PEDRO MARIN 0424-3796429</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>10.515344443532122, -66.89849652348983</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>LIBERTADOR</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>San Bernardino</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SUBLETTE</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Edificio Villa Savoya</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Edificio Privado</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>34</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>34</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="n">
+        <v>76</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Avenida Sublett, Comuna Gran Cacique Paramaconi</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>FUNDACARACAS</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Arq. Víctor Miguel Cañas Villarreal 0412-9844777</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gilberto Moncada</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>10.51475717689199, -66.89908338244686</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>SAN BERNARDINO</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>LOS PROCERES</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Edificio Alfa</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Circuito comunal 1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>MOISES</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>Alcaldía de Caracas</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Edificio Privado</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>4</v>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>14</v>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>Apartamento</t>
         </is>
       </c>
-      <c r="N21" t="n">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>14</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>13</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Av Anauco</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>FUNDACARACAS</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Arq. Víctor Miguel Cañas Villarreal 0412-9844777</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>José Ramon Perez 04142622624</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>10.514776561597898, -66.90304557490295</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
         <v>0</v>
       </c>
-      <c r="O21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="n">
-        <v>4</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Av. Principal de Residencia Anauco</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Brisopp y Paneles Caracas</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Orlando Tarazona (0414) 351.0959.</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Rafael Quijada</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="n">
-        <v>21</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>LIBERTADOR</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>SAN BERNARDINO</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>PARQUE RESIDENCIAL ANAUCO</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ELITE</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Circuito comunal 1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Edificio San José</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>Alcaldía de Caracas</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Edificio Privado</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>60</v>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>8</v>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>Apartamento</t>
         </is>
       </c>
-      <c r="N22" t="n">
-        <v>60</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="n">
-        <v>60</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>AVENIDA LOS PROCERES CON AV MARQUES DEL TORO, URB SAN BERNARDINO</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>BARWILL GONZALEZ 0414-1243722</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>SORISBEL ARAUJO 0414-1343322</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="n">
-        <v>22</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="M27" t="n">
+        <v>8</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>8</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Av Los Proceres</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>FONDEC</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dileidy Ortiz 0414-2540410</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>10.51397056236837, -66.9074602440866</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>LIBERTADOR</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>SAN BERNARDINO</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>AV. LOS PRÓCERES</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MAROA</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAN BERNARDINO </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AVENIDA LOS PROCERES</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CORAZÓN DE JESUS</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>Alcaldía de Caracas</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Edificio Privado</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>19</v>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>13</v>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>Apartamento</t>
         </is>
       </c>
-      <c r="N23" t="n">
-        <v>19</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="n">
-        <v>19</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>AVENIDA LOS PROCERES, URB SAN BERNARDINO</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>BARWILL GONZALEZ 0414-1243722</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>JORGE BECERRA 0424-6749271</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="n">
-        <v>23</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="M28" t="n">
+        <v>13</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>13</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AVENIDA LOS PRÓCERES </t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>PROHABITAT LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>JOSE GREGORIO ROJAS EUGENIO 04141916837</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANDRA HERNÁNDEZ </t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>10.514934060457499, -66.89717851866098</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>LIBERTADOR</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>SAN BERNARDINO</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>AV. LOS PRÓCERES</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MACTOR</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Edificio Privado</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>22</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>22</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="n">
-        <v>22</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>AVENIDA LOS PROCERES, URB SAN BERNARDINO</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>BARWILL GONZALEZ 0414-1243722</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>PEDRO MARIN 0424-3796429</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="n">
-        <v>24</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>San Bernardino</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>SUBLETTE</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Edificio Villa Savoya</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Edificio Privado</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>34</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>34</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="n">
-        <v>76</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Avenida Sublett, Comuna Gran Cacique Paramaconi</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>FUNDACARACAS</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Arq. Víctor Miguel Cañas Villarreal 0412-9844777</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Gilberto Moncada</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="n">
-        <v>25</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>SAN BERNARDINO</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Circuito comunal 1</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>MOISES</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Edificio Privado</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>14</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="R26" t="n">
-        <v>13</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>Av Anauco</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>FUNDACARACAS</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Arq. Víctor Miguel Cañas Villarreal 0412-9844777</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>José Ramon Perez 04142622624</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="n">
-        <v>26</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>SAN BERNARDINO</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Circuito comunal 1</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Edificio San José</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Edificio Privado</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>8</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>8</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="n">
-        <v>8</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>Av Los Proceres</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>FONDEC</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Dileidy Ortiz 0414-2540410</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="n">
-        <v>27</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SAN BERNARDINO </t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>AVENIDA LOS PROCERES</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>CORAZÓN DE JESUS</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Edificio Privado</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>13</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N28" t="n">
-        <v>13</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="n">
-        <v>13</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AVENIDA LOS PRÓCERES </t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>PROHABITAT LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>JOSE GREGORIO ROJAS EUGENIO 04141916837</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANDRA HERNÁNDEZ </t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LIBERTADOR</t>
+          <t>SAN JUAN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SAN JUAN</t>
+          <t>ARTIGAS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
-        <is>
-          <t>ARTIGAS</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
         <is>
           <t>OPPE 44
 28 de Julio</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Urbanismo GMVV </t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>AV SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>BARWILL GONZALEZ 0414-1243722</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>10.492989481440796, -66.93729670113483</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SAN PEDRO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edificio America </t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>Alcaldía de Caracas</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Edificio Privado</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>AV NUEVA GRANDA</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>PROTECCIÓN CIVIL</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>DAVID LOPEZ 416-6121721</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>10.476423387128055, -66.8971961666293</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SANTA ROSALIA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CASCO CENTRAL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>OPPE 10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">Urbanismo GMVV </t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>Apartamento</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>AV SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>BARWILL GONZALEZ 0414-1243722</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="n">
-        <v>29</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>ESQUINA DE SANTA ROSALIA ACANDELITO</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>PROTECCIÓN CIVIL</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>DAVID LOPEZ 416-6121721</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>10.497903811938677, -66.91404653574409</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>LIBERTADOR</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>SAN PEDRO</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Edificio America </t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Edificio Privado</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>AV NUEVA GRANDA</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>PROTECCIÓN CIVIL</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>DAVID LOPEZ 416-6121721</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="n">
-        <v>30</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>SANTA ROSALIA</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>CASCO CENTRAL</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>OPPE 10</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Urbanismo GMVV </t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>ESQUINA DE SANTA ROSALIA ACANDELITO</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>PROTECCIÓN CIVIL</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>DAVID LOPEZ 416-6121721</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="n">
-        <v>31</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SANTA ROSALIA</t>
+          <t>ESQUINA CORDOBA A CRISTO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
-        <is>
-          <t>ESQUINA CORDOBA A CRISTO</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
         <is>
           <t>OPPE 47
 Rey de Reyes</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Urbanismo GMVV </t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>96</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>96</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="n">
+        <v>115</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>ESQUINA CORDOBA A EL CRISTO URBANISMO REY DE REYES</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>BARWILL GONZALEZ 0414-1243722</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>NELLY 0412-3350083</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	
+10.49846728628692, -66.90977600093112</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Santa Rosalia</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CASCO CENTRAL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>OPPE 11  El Gigante de Latinoamerica</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>Alcaldía de Caracas</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t xml:space="preserve">Urbanismo GMVV </t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>64</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>15</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Avenidad Este 12 Esquina el Viento</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Cuerpo de Ingenieros de la GNB (DICOI N° 43)</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>May. Delgado Ramirez Angel Jose 0424-4059210</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Blanca Liset Lopez Orozco</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>10.49856524414421, -66.91211992650233</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SANTA ROSALIA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CASCO CENTRAL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Cilyex</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Edificio Privado</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> esquina Viento a Muerto </t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>IMGRAD</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>IVAN MARTINEZ - 0412-0279209</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Eduardo Pérez  - 04264233002</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>10.497094498827074, -66.9121884757819</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SANTA TERESA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CANDILITO</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Edif Centro Residencial Castán</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Edificio Privado</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>109</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>109</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Ubicado esquina de Castán candilito</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>IMGRAD</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>IVAN MARTINEZ - 0412-0279209</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Freddy rondón 0412 382.25.52</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>10.497596468325467, -66.91548701654848</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SANTA TERESA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>OPPE 8</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Urbanismo GMVV </t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
         <v>96</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>Apartamento</t>
         </is>
       </c>
-      <c r="N32" t="n">
-        <v>96</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="n">
-        <v>115</v>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>ESQUINA CORDOBA A EL CRISTO URBANISMO REY DE REYES</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
+      <c r="M36" t="n">
+        <v>41</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="n">
+        <v>41</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Esquina de velazquez sur 1</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>PLANIFICACIÓ Y CONTROL URBANO</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Cesar Martínez Bolívar 0422-4050818</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>10.500319, -66.914059</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SANTA TERESA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>OPPE 9</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Urbanismo GMVV </t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>144</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>30</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="n">
+        <v>30</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Esquina de velazquez sur 1</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>PLANIFICACIÓ Y CONTROL URBANO</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Cesar Martínez Bolívar 0422-4050818</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>10.498469154806708, -66.91494269691273</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SANTA TERESA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PLAZA LA CONCORDIA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>OPPE 57</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alcaldía de Caracas</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Urbanismo GMVV </t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>48</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>48</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="n">
+        <v>48</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Por la Plaza la Concordia</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
         <is>
           <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>BARWILL GONZALEZ 0414-1243722</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>NELLY 0412-3350083</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="n">
-        <v>32</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>10.498356402935032, -66.91750609281524</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>LIBERTADOR</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Santa Rosalia</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>CASCO CENTRAL</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>OPPE 11  El Gigante de Latinoamerica</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SANTA TERESA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PLAZA LA CONCORDIA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>OPPE 58</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>Alcaldía de Caracas</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">Urbanismo GMVV </t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>64</v>
-      </c>
-      <c r="M33" t="inlineStr">
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>48</v>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>Apartamento</t>
         </is>
       </c>
-      <c r="N33" t="n">
-        <v>15</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>76 (Poblacion 260)</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>Avenidad Este 12 Esquina el Viento</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Cuerpo de Ingenieros de la GNB (DICOI N° 43)</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>May. Delgado Ramirez Angel Jose 0424-4059210</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Blanca Liset Lopez Orozco</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="n">
-        <v>33</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="M39" t="n">
+        <v>48</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="n">
+        <v>48</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Por la Plaza la Concordia</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>BARWILL GONZALEZ 0414-1243722</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>10.500257075470612, -66.9150046434567</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>LIBERTADOR</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>SANTA ROSALIA</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>CASCO CENTRAL</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Cilyex</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SUCRE</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>BARRIO ISAIAS MEDINA ANGARITA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Edificio Pasaje 17</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>Alcaldía de Caracas</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Edificio Privado</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>16</v>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>Apartamento</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> esquina Viento a Muerto </t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
+      <c r="M40" t="n">
+        <v>16</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="n">
+        <v>19</v>
+      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
         <is>
           <t>IMGRAD</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>IVAN MARTINEZ - 0412-0279209</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Eduardo Pérez  - 04264233002</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="n">
-        <v>34</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>10.509101172728707, -66.96391008735873</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>LIBERTADOR</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>SANTA TERESA</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>CANDILITO</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Edif Centro Residencial Castán</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SUCRE</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>EL LÍMON</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edificio Lamas </t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>Alcaldía de Caracas</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Edificio Privado</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>109</v>
-      </c>
-      <c r="M35" t="inlineStr">
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>9</v>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>Apartamento</t>
         </is>
       </c>
-      <c r="N35" t="n">
-        <v>109</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>Ubicado esquina de Castán candilito</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>IMGRAD</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>IVAN MARTINEZ - 0412-0279209</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Freddy rondón 0412 382.25.52</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="n">
-        <v>35</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>SANTA TERESA</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>OPPE 8</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Urbanismo GMVV </t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>96</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>41</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="n">
-        <v>41</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>Esquina de velazquez sur 1</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>PLANIFICACIÓ Y CONTROL URBANO</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Cesar Martínez Bolívar 0422-4050818</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="n">
-        <v>36</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>SANTA TERESA</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>OPPE 9</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Urbanismo GMVV </t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="n">
-        <v>144</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N37" t="n">
-        <v>30</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="n">
-        <v>30</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>Esquina de velazquez sur 1</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>PLANIFICACIÓ Y CONTROL URBANO</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Cesar Martínez Bolívar 0422-4050818</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="n">
-        <v>37</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>SANTA TERESA</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>PLAZA LA CONCORDIA</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>OPPE 57</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Urbanismo GMVV </t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>48</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N38" t="n">
-        <v>48</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="n">
-        <v>48</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>Por la Plaza la Concordia</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>BARWILL GONZALEZ 0414-1243722</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="n">
-        <v>38</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>SANTA TERESA</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>PLAZA LA CONCORDIA</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>OPPE 58</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Urbanismo GMVV </t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" t="n">
-        <v>48</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>48</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="n">
-        <v>48</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>Por la Plaza la Concordia</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>CORPORACION DE SERVICIOS MUNICIPALES LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>BARWILL GONZALEZ 0414-1243722</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="n">
-        <v>39</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>SUCRE</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>BARRIO ISAIAS MEDINA ANGARITA</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Edificio Pasaje 17</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Edificio Privado</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="n">
-        <v>16</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>16</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="n">
-        <v>19</v>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>IMGRAD</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>IVAN MARTINEZ - 0412-0279209</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="n">
-        <v>40</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>DISTRITO CAPITAL</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>SUCRE</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>EL LÍMON</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Edificio Lamas </t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Edificio Privado</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>9</v>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
       <c r="N41" t="n">
-        <v>9</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q41" t="n">
         <v>14</v>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Carretera Caracas la Guaira</t>
+        </is>
+      </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Carretera Caracas la Guaira</t>
+          <t>PROHABITAT LIBERTADOR</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
-        <is>
-          <t>PROHABITAT LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
         <is>
           <t>Maria Rodriguez
 04146100416</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>ROSA AMARISTA 
 04264170836</t>
         </is>
       </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>10.530033388074242, -66.97718836903289</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
       <c r="B42" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DISTRITO CAPITAL</t>
+          <t>LIBERTADOR</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LIBERTADOR</t>
+          <t>SUCRE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SUCRE</t>
+          <t>EL LÍMON</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>EL LÍMON</t>
+          <t>2 viviendas Carretera vieja Caracas - La Guaira</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2 viviendas Carretera vieja Caracas - La Guaira</t>
+          <t>Alcaldía de Caracas</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
           <t>Caserio</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>2</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
         <v>0</v>
       </c>
-      <c r="L42" t="n">
+      <c r="Q42" t="n">
         <v>2</v>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>casa</t>
-        </is>
-      </c>
-      <c r="N42" t="n">
-        <v>2</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="n">
-        <v>2</v>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Carretera Caracas la Guaira</t>
+        </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Carretera Caracas la Guaira</t>
+          <t>PROHABITAT LIBERTADOR</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
-        <is>
-          <t>PROHABITAT LIBERTADOR</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
         <is>
           <t>Maria Rodriguez
 04146100416</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>ROSA AMARISTA 
 04264170836</t>
         </is>
       </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>10.530617969753001, -66.95989810516429</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
       <c r="B43" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DISTRITO CAPITAL</t>
+          <t>LIBERTADOR</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LIBERTADOR</t>
+          <t>SUCRE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SUCRE</t>
+          <t>La Silsa</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>La Silsa</t>
+          <t>12 VIVIENDAS DE LA SILSA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>12 VIVIENDAS DE LA SILSA</t>
+          <t>Alcaldía de Caracas</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Alcaldía de Caracas</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
           <t>Caserio</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
         <is>
           <t>Casa</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" t="n">
+        <v>12</v>
+      </c>
       <c r="P43" t="n">
-        <v>12</v>
+        <v>0.06</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="R43" t="n">
         <v>18</v>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>sector la silsa, calle, Ezequiel Zamora</t>
+        </is>
+      </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>sector la silsa, calle, Ezequiel Zamora</t>
+          <t>INTRAVIALCA</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>INTRAVIALCA</t>
+          <t>Stefanny Briceño 0424-7058019</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>Stefanny Briceño 0424-7058019</t>
+          <t>Yasmira Sánchez 0412962 6648</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Yasmira Sánchez 0412962 6648</t>
+          <t>10.502078335221537, -66.95077012900992</t>
         </is>
       </c>
     </row>

--- a/MATRIZ_MAESTRA_DECISIONES_Trazabilidad.xlsx
+++ b/MATRIZ_MAESTRA_DECISIONES_Trazabilidad.xlsx
@@ -1350,7 +1350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1368,11 +1368,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>AMARILLO</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
+      <c r="B3" t="n">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NEGRO</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/MATRIZ_MAESTRA_DECISIONES_Trazabilidad.xlsx
+++ b/MATRIZ_MAESTRA_DECISIONES_Trazabilidad.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,7 +525,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1305,37 +1305,11 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>FUNDACARACAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Santa Rosalia</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>CASCO CENTRAL</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Cuerpo de Ingenieros de la GNB (DICOI N° 43)</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1567,7 @@
         <v>8</v>
       </c>
       <c r="P2" t="n">
-        <v>83</v>
+        <v>0.83</v>
       </c>
       <c r="Q2" t="n">
         <v>98</v>
@@ -1758,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1766,15 +1740,17 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N4" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0.92</v>
+      </c>
       <c r="Q4" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1932,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1940,13 +1916,15 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N6" t="n">
-        <v>0.47</v>
+        <v>0.62</v>
       </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0.99</v>
+      </c>
       <c r="Q6" t="n">
         <v>25</v>
       </c>
@@ -2018,10 +1996,10 @@
         <v>14</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>288</v>
+        <v>24</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -2029,15 +2007,19 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1</v>
+      </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -2179,34 +2161,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Caserio</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>casa</t>
+          <t>Apartamento</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
         <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4</v>
+        <v>0.54</v>
       </c>
       <c r="Q9" t="n">
         <v>6</v>
@@ -2363,29 +2343,33 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
         <v>5</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>casa</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+        <v>0.51</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.99</v>
+      </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2468,7 +2452,7 @@
         <v>300</v>
       </c>
       <c r="N12" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -2552,7 +2536,7 @@
         <v>300</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -2640,7 +2624,7 @@
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2816,7 +2800,7 @@
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2886,13 +2870,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K17" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -2903,10 +2887,14 @@
         <v>23</v>
       </c>
       <c r="N17" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+        <v>0.6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>13</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.76</v>
+      </c>
       <c r="Q17" t="n">
         <v>13</v>
       </c>
@@ -2974,10 +2962,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K18" t="n">
         <v>240</v>
@@ -2991,10 +2979,12 @@
         <v>240</v>
       </c>
       <c r="N18" t="n">
-        <v>0.16</v>
+        <v>0.46</v>
       </c>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>0.92</v>
+      </c>
       <c r="Q18" t="n">
         <v>266</v>
       </c>
@@ -3079,7 +3069,7 @@
         <v>300</v>
       </c>
       <c r="N19" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -3149,7 +3139,7 @@
         <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
         <v>144</v>
@@ -3160,15 +3150,19 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>12</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
       <c r="Q20" t="n">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -3240,7 +3234,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -3251,12 +3245,12 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -3336,15 +3330,19 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="N22" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+        <v>0.44</v>
+      </c>
+      <c r="O22" t="n">
+        <v>28</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.78</v>
+      </c>
       <c r="Q22" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -3427,10 +3425,12 @@
         <v>19</v>
       </c>
       <c r="N23" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>0.86</v>
+      </c>
       <c r="Q23" t="n">
         <v>19</v>
       </c>
@@ -3515,10 +3515,12 @@
         <v>22</v>
       </c>
       <c r="N24" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>0.86</v>
+      </c>
       <c r="Q24" t="n">
         <v>22</v>
       </c>
@@ -3592,7 +3594,7 @@
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -3600,15 +3602,19 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+        <v>0.57</v>
+      </c>
+      <c r="O25" t="n">
+        <v>10</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
       <c r="Q25" t="n">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -3688,12 +3694,14 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="O26" t="n">
         <v>14</v>
       </c>
       <c r="P26" t="n">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
       <c r="Q26" t="n">
         <v>13</v>
@@ -3779,7 +3787,7 @@
         <v>8</v>
       </c>
       <c r="N27" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -4098,7 +4106,9 @@
       <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>98</v>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -4111,7 +4121,7 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -4188,13 +4198,15 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="N32" t="n">
-        <v>0.16</v>
+        <v>0.46</v>
       </c>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>0.92</v>
+      </c>
       <c r="Q32" t="n">
         <v>115</v>
       </c>
@@ -4239,7 +4251,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Santa Rosalia</t>
+          <t>SANTA ROSALIA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4277,13 +4289,15 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N33" t="n">
-        <v>0.7</v>
+        <v>0.96</v>
       </c>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
@@ -4367,9 +4381,11 @@
         <v>0.08</v>
       </c>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>0.3</v>
+      </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -4536,12 +4552,14 @@
         <v>41</v>
       </c>
       <c r="N36" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>0.9</v>
+      </c>
       <c r="Q36" t="n">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -4697,13 +4715,15 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="N38" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>0.35</v>
+      </c>
       <c r="Q38" t="n">
         <v>48</v>
       </c>
@@ -4781,13 +4801,15 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N39" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q39" t="n">
         <v>48</v>
       </c>
@@ -4871,7 +4893,9 @@
         <v>0.1</v>
       </c>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>0.95</v>
+      </c>
       <c r="Q40" t="n">
         <v>19</v>
       </c>
@@ -5040,7 +5064,7 @@
         <v>2</v>
       </c>
       <c r="N42" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
@@ -5127,12 +5151,14 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>0.39</v>
+      </c>
       <c r="O43" t="n">
         <v>12</v>
       </c>
       <c r="P43" t="n">
-        <v>0.06</v>
+        <v>0.38</v>
       </c>
       <c r="Q43" t="n">
         <v>18</v>
